--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_CB ALGECIRAS.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_CB ALGECIRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>D. RAMIREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,73 +553,73 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8868</v>
+        <v>6.2648</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4605</v>
+        <v>5.602600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4263</v>
+        <v>0.6621000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.857100000000001</v>
+        <v>-1.9122</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.2894</v>
+        <v>-2.5296</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4323</v>
+        <v>0.6173000000000002</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7639000000000005</v>
+        <v>2.166</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.7585</v>
+        <v>1.8669</v>
       </c>
       <c r="L2" t="n">
-        <v>3.5223</v>
+        <v>0.2992</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.621099999999999</v>
+        <v>-4.0783</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.531000000000001</v>
+        <v>-4.396599999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.08999999999999986</v>
+        <v>0.3183000000000002</v>
       </c>
       <c r="P2" t="n">
-        <v>5.8496</v>
+        <v>3.8997</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9749</v>
+        <v>-3.3148</v>
       </c>
       <c r="R2" t="n">
-        <v>6.8246</v>
+        <v>7.214399999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9274</v>
+        <v>0.5664</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3814</v>
+        <v>-0.4103</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4539</v>
+        <v>0.9767000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8217</v>
+        <v>3.7108</v>
       </c>
       <c r="W2" t="n">
-        <v>5.053</v>
+        <v>7.1615</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2312000000000001</v>
+        <v>-3.4507</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. RAMIREZ SANCHEZ</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -631,67 +631,67 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0421</v>
+        <v>5.8868</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3801</v>
+        <v>3.4605</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6621000000000001</v>
+        <v>2.4263</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.1347</v>
+        <v>-3.857100000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.1447</v>
+        <v>-7.2894</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009800000000000253</v>
+        <v>3.4323</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9434999999999999</v>
+        <v>0.7639000000000005</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2519</v>
+        <v>-2.7585</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3084000000000001</v>
+        <v>3.5223</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.0783</v>
+        <v>-4.621099999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.396599999999999</v>
+        <v>-4.531000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3183000000000002</v>
+        <v>-0.08999999999999986</v>
       </c>
       <c r="P3" t="n">
-        <v>3.8997</v>
+        <v>5.8496</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.3148</v>
+        <v>-0.9749</v>
       </c>
       <c r="R3" t="n">
-        <v>7.214399999999999</v>
+        <v>6.8246</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5664</v>
+        <v>-0.9274</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4103</v>
+        <v>-1.3814</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9767000000000001</v>
+        <v>0.4539</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7108</v>
+        <v>4.8217</v>
       </c>
       <c r="W3" t="n">
-        <v>7.1615</v>
+        <v>5.053</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.4507</v>
+        <v>-0.2312000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1087,7 +1087,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1096,76 +1096,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2225</v>
+        <v>-1.3793</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2225</v>
+        <v>-0.9461999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.4330000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2225</v>
+        <v>-1.1564</v>
       </c>
       <c r="H9" t="n">
-        <v>0.615</v>
+        <v>-2.1948</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6075</v>
+        <v>1.0385</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2225</v>
+        <v>0.6783000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.615</v>
+        <v>1.1732</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6075</v>
+        <v>-0.4950000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.8348</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-3.368</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.5334</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.3398</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9247</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5.264699999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-1.1516</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1.087</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.06469999999999998</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.4111</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3873</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.7984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1174,76 +1174,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3793</v>
+        <v>-4.466</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9461999999999999</v>
+        <v>-2.9246</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4330000000000001</v>
+        <v>-1.5414</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1564</v>
+        <v>-1.7013</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1948</v>
+        <v>-1.1036</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0385</v>
+        <v>-0.5975999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6783000000000001</v>
+        <v>1.0888</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1732</v>
+        <v>0.8863000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4950000000000001</v>
+        <v>0.2025</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8348</v>
+        <v>-2.7899</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.368</v>
+        <v>-1.9898</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5334</v>
+        <v>-0.8001</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3398</v>
+        <v>-3.1197</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9247</v>
+        <v>-5.069599999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>5.264699999999999</v>
+        <v>1.9499</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1516</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.087</v>
+        <v>0.1677</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.06469999999999998</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4111</v>
+        <v>-0.3209</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3873</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.7984</v>
+        <v>-1.2095</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1252,76 +1252,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.466</v>
+        <v>-7.3149</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9246</v>
+        <v>-5.5857</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5414</v>
+        <v>-1.7293</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7013</v>
+        <v>-6.147600000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1036</v>
+        <v>-6.4778</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5975999999999999</v>
+        <v>0.3302</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0888</v>
+        <v>-2.8833</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8863000000000001</v>
+        <v>-3.3198</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2025</v>
+        <v>0.4366000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7899</v>
+        <v>-3.2644</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9898</v>
+        <v>-3.158</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8001</v>
+        <v>-0.1064</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1197</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.069599999999999</v>
+        <v>-4.0947</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9499</v>
+        <v>4.0947</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6759999999999999</v>
+        <v>-1.0983</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1677</v>
+        <v>-1.0478</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5082000000000001</v>
+        <v>-0.05039999999999994</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3209</v>
+        <v>-0.06909999999999994</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8885999999999999</v>
+        <v>2.4402</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2095</v>
+        <v>-2.5093</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>T. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,73 +1333,73 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.3149</v>
+        <v>-8.685600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5857</v>
+        <v>-6.1178</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7293</v>
+        <v>-2.5678</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.147600000000001</v>
+        <v>-3.5816</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.4778</v>
+        <v>-1.4756</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3302</v>
+        <v>-2.1061</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.8833</v>
+        <v>-2.976</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.3198</v>
+        <v>-1.2585</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4366000000000001</v>
+        <v>-1.7175</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2644</v>
+        <v>-0.6056</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.158</v>
+        <v>-0.2171</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1064</v>
+        <v>-0.3885</v>
       </c>
       <c r="P12" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0.5849000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.0947</v>
+        <v>-1.9498</v>
       </c>
       <c r="R12" t="n">
-        <v>4.0947</v>
+        <v>2.5349</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0983</v>
+        <v>-1.5775</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0478</v>
+        <v>-1.1918</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.05039999999999994</v>
+        <v>-0.3856999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.06909999999999994</v>
+        <v>-4.111499999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4402</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.5093</v>
+        <v>-4.111499999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. VAN BRANDWIJK</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,73 +1411,73 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.685600000000001</v>
+        <v>-10.2037</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1178</v>
+        <v>-6.9557</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5678</v>
+        <v>-3.2483</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.5816</v>
+        <v>-3.1309</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4756</v>
+        <v>-8.196400000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1061</v>
+        <v>5.065499999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.976</v>
+        <v>2.9705</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2585</v>
+        <v>-3.5329</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7175</v>
+        <v>6.503399999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6056</v>
+        <v>-6.1014</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2171</v>
+        <v>-4.6636</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3885</v>
+        <v>-1.4379</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5849000000000001</v>
+        <v>-3.7047</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9498</v>
+        <v>-9.9443</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5349</v>
+        <v>6.2395</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5775</v>
+        <v>-0.4216</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1918</v>
+        <v>-1.096</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3856999999999999</v>
+        <v>0.6744999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.111499999999999</v>
+        <v>-2.9465</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1143</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.111499999999999</v>
+        <v>-4.0608</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,144 +1489,66 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.2037</v>
+        <v>-3.352</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.9557</v>
+        <v>1.4056</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2483</v>
+        <v>-4.7577</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.1309</v>
+        <v>-15.2893</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.196400000000001</v>
+        <v>-32.7848</v>
       </c>
       <c r="I14" t="n">
-        <v>5.065499999999999</v>
+        <v>17.4959</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9705</v>
+        <v>27.46700000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.5329</v>
+        <v>6.365400000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>6.503399999999999</v>
+        <v>21.1012</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.1014</v>
+        <v>-42.7563</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.6636</v>
+        <v>-39.1508</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4379</v>
+        <v>-3.6054</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.7047</v>
+        <v>12.674</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.9443</v>
+        <v>-48.7463</v>
       </c>
       <c r="R14" t="n">
-        <v>6.2395</v>
+        <v>61.42059999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4216</v>
+        <v>-3.3496</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.096</v>
+        <v>-8.9194</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6744999999999999</v>
+        <v>5.5697</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.9465</v>
+        <v>2.612600000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1143</v>
+        <v>31.6051</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.0608</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CB ALGECIRAS</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-3.3522</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.4056</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-4.7577</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-15.2893</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-32.78490000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>17.4959</v>
-      </c>
-      <c r="J15" t="n">
-        <v>27.467</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.365399999999999</v>
-      </c>
-      <c r="L15" t="n">
-        <v>21.1011</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-42.7563</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-39.1508</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-3.6054</v>
-      </c>
-      <c r="P15" t="n">
-        <v>12.674</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-48.7463</v>
-      </c>
-      <c r="R15" t="n">
-        <v>61.42059999999999</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-3.3496</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-8.9194</v>
-      </c>
-      <c r="U15" t="n">
-        <v>5.5697</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.612600000000001</v>
-      </c>
-      <c r="W15" t="n">
-        <v>31.6051</v>
-      </c>
-      <c r="X15" t="n">
         <v>-28.9923</v>
       </c>
     </row>
